--- a/data/trans_camb/P1423-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1423-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 3,09</t>
+          <t>-0,29; 3,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,11</t>
+          <t>-1,37; 2,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 7,95</t>
+          <t>3,13; 7,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,59; 9,66</t>
+          <t>3,41; 9,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 8,35</t>
+          <t>2,23; 8,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 6,62</t>
+          <t>0,75; 6,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,75</t>
+          <t>2,16; 5,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,64</t>
+          <t>1,15; 4,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,44</t>
+          <t>3,02; 6,5</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 198,71</t>
+          <t>-15,07; 206,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,25; 131,32</t>
+          <t>-48,48; 116,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90,79; 492,01</t>
+          <t>90,78; 473,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42,68; 173,63</t>
+          <t>42,23; 187,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,77; 155,06</t>
+          <t>27,62; 163,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,32; 122,58</t>
+          <t>9,43; 129,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,28; 156,64</t>
+          <t>40,2; 163,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,3; 125,99</t>
+          <t>23,24; 130,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51,62; 176,48</t>
+          <t>59,4; 178,08</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 3,6</t>
+          <t>-0,12; 3,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,58</t>
+          <t>-2,14; 0,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,8</t>
+          <t>-1,59; 2,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 6,58</t>
+          <t>0,76; 6,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 4,0</t>
+          <t>-1,35; 3,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 6,0</t>
+          <t>1,03; 6,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,32</t>
+          <t>0,98; 4,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,74</t>
+          <t>-1,19; 1,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,44</t>
+          <t>-0,66; 3,56</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 163,72</t>
+          <t>-3,85; 171,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,41; 29,92</t>
+          <t>-57,01; 36,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,48; 113,66</t>
+          <t>-37,8; 126,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,38; 102,09</t>
+          <t>8,4; 94,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 63,5</t>
+          <t>-15,16; 54,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,29; 92,27</t>
+          <t>10,57; 93,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,18; 95,93</t>
+          <t>17,51; 94,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 37,9</t>
+          <t>-19,48; 39,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 70,96</t>
+          <t>-10,06; 77,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 1,79</t>
+          <t>-2,14; 1,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,99</t>
+          <t>-1,84; 2,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,94</t>
+          <t>0,25; 4,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,04</t>
+          <t>-0,88; 5,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,12</t>
+          <t>-1,5; 4,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 6,64</t>
+          <t>-3,46; 6,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 2,79</t>
+          <t>-0,76; 2,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,52</t>
+          <t>-1,04; 2,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 4,89</t>
+          <t>-0,5; 4,91</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-53,49; 68,6</t>
+          <t>-50,35; 78,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-43,41; 78,74</t>
+          <t>-41,26; 80,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,43; 180,89</t>
+          <t>-1,03; 174,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 76,73</t>
+          <t>-10,26; 76,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 63,28</t>
+          <t>-16,66; 66,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,02; 96,39</t>
+          <t>-37,99; 93,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 56,77</t>
+          <t>-11,33; 59,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 53,53</t>
+          <t>-15,41; 50,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 94,71</t>
+          <t>-4,36; 99,36</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,08</t>
+          <t>-0,69; 3,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,88</t>
+          <t>-0,87; 2,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,2</t>
+          <t>1,4; 5,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,95</t>
+          <t>0,82; 6,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,9</t>
+          <t>0,27; 5,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 6,42</t>
+          <t>1,09; 6,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,97</t>
+          <t>0,76; 3,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,89</t>
+          <t>0,57; 3,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,3</t>
+          <t>1,97; 5,42</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,33; 113,44</t>
+          <t>-17,91; 108,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 100,14</t>
+          <t>-22,42; 108,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26,96; 184,14</t>
+          <t>29,91; 202,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,1; 86,94</t>
+          <t>8,38; 89,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,38; 85,89</t>
+          <t>1,69; 84,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,26; 95,76</t>
+          <t>12,01; 96,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,58; 78,3</t>
+          <t>11,28; 76,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,97; 78,33</t>
+          <t>8,82; 70,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>28,87; 103,46</t>
+          <t>29,25; 105,23</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,07</t>
+          <t>0,09; 1,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,96</t>
+          <t>-0,68; 0,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,7</t>
+          <t>1,29; 3,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,09</t>
+          <t>2,34; 5,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,95</t>
+          <t>1,13; 4,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,04</t>
+          <t>1,16; 4,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,34</t>
+          <t>1,62; 3,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,17</t>
+          <t>0,68; 2,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,09</t>
+          <t>1,88; 4,14</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5,29; 74,33</t>
+          <t>1,93; 73,93</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,24; 36,47</t>
+          <t>-18,91; 34,96</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39,35; 137,32</t>
+          <t>38,28; 132,47</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27,61; 73,02</t>
+          <t>28,59; 76,61</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>13,9; 56,6</t>
+          <t>13,83; 60,88</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,09; 69,94</t>
+          <t>16,31; 69,48</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,76; 65,9</t>
+          <t>27,85; 64,98</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9,31; 44,22</t>
+          <t>11,55; 45,31</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>33,4; 81,69</t>
+          <t>33,54; 82,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1423-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1423-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,32</t>
+          <t>5,24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>4,7</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,76</t>
+          <t>5,04</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,17</t>
+          <t>-0,45; 3,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 2,06</t>
+          <t>-1,18; 2,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 7,71</t>
+          <t>2,91; 7,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,41; 9,56</t>
+          <t>3,57; 9,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 8,41</t>
+          <t>2,18; 8,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,68</t>
+          <t>2,31; 7,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,94</t>
+          <t>1,99; 5,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,65</t>
+          <t>1,02; 4,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 6,5</t>
+          <t>3,28; 6,8</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>226,49%</t>
+          <t>223,31%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>108,03%</t>
+          <t>114,28%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 206,44</t>
+          <t>-17,92; 182,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-48,48; 116,62</t>
+          <t>-40,18; 129,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90,78; 473,7</t>
+          <t>84,74; 478,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42,23; 187,61</t>
+          <t>43,57; 181,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,62; 163,27</t>
+          <t>28,44; 158,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,43; 129,01</t>
+          <t>27,34; 139,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,2; 163,4</t>
+          <t>37,55; 155,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,24; 130,23</t>
+          <t>19,25; 124,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59,4; 178,08</t>
+          <t>59,54; 185,43</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>1,74</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,55</t>
+          <t>3,46</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>2,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,65</t>
+          <t>-0,17; 3,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,71</t>
+          <t>-2,13; 0,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,92</t>
+          <t>0,07; 3,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,22</t>
+          <t>0,99; 6,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,65</t>
+          <t>-1,38; 3,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 6,1</t>
+          <t>1,04; 5,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,3</t>
+          <t>0,88; 4,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,8</t>
+          <t>-1,28; 1,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,56</t>
+          <t>1,17; 4,05</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>48,92%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 171,38</t>
+          <t>-5,37; 171,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,01; 36,2</t>
+          <t>-57,68; 30,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,8; 126,38</t>
+          <t>1,16; 164,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,4; 94,87</t>
+          <t>9,87; 97,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 54,99</t>
+          <t>-15,27; 56,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,57; 93,05</t>
+          <t>10,89; 91,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,51; 94,97</t>
+          <t>13,24; 93,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,48; 39,09</t>
+          <t>-20,46; 42,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 77,14</t>
+          <t>18,54; 90,34</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>2,08</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,56</t>
+          <t>5,83</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,74</t>
+          <t>3,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,88</t>
+          <t>-2,1; 1,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,0</t>
+          <t>-1,72; 2,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 4,89</t>
+          <t>0,09; 4,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 5,22</t>
+          <t>-1,23; 4,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 4,33</t>
+          <t>-1,81; 4,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 6,58</t>
+          <t>2,88; 8,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,84</t>
+          <t>-0,95; 2,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,46</t>
+          <t>-1,01; 2,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 4,91</t>
+          <t>2,12; 5,9</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-50,35; 78,76</t>
+          <t>-50,22; 69,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,26; 80,56</t>
+          <t>-39,5; 80,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 174,24</t>
+          <t>-2,22; 168,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 76,81</t>
+          <t>-12,59; 72,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 66,74</t>
+          <t>-20,38; 67,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,99; 93,36</t>
+          <t>30,69; 135,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 59,63</t>
+          <t>-14,43; 57,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 50,69</t>
+          <t>-15,32; 51,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 99,36</t>
+          <t>31,92; 121,79</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>3,43</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,95</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,72</t>
+          <t>4,15</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,04</t>
+          <t>-0,75; 3,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,9</t>
+          <t>-0,78; 2,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,51</t>
+          <t>1,72; 5,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 6,16</t>
+          <t>0,82; 6,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 5,78</t>
+          <t>0,42; 5,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 6,49</t>
+          <t>2,21; 7,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,99</t>
+          <t>0,73; 4,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,67</t>
+          <t>0,52; 3,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,42</t>
+          <t>2,45; 5,63</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>70,89%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 108,32</t>
+          <t>-19,65; 109,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,42; 108,21</t>
+          <t>-18,84; 102,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,91; 202,4</t>
+          <t>31,94; 197,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,38; 89,15</t>
+          <t>8,91; 91,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,69; 84,18</t>
+          <t>2,57; 87,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,01; 96,99</t>
+          <t>21,11; 104,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,28; 76,09</t>
+          <t>10,73; 78,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,82; 70,87</t>
+          <t>6,91; 71,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29,25; 105,23</t>
+          <t>36,45; 110,4</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>2,99</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>4,61</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>3,85</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,98</t>
+          <t>0,1; 2,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,94</t>
+          <t>-0,74; 1,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,7</t>
+          <t>1,95; 4,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,24</t>
+          <t>2,49; 5,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,07</t>
+          <t>1,12; 3,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,9</t>
+          <t>3,37; 6,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,31</t>
+          <t>1,65; 3,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,28</t>
+          <t>0,54; 2,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,14</t>
+          <t>2,99; 4,66</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>71,54%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1,93; 73,93</t>
+          <t>0,43; 74,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 34,96</t>
+          <t>-21,42; 38,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>38,28; 132,47</t>
+          <t>54,72; 152,84</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28,59; 76,61</t>
+          <t>30,21; 74,69</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>13,83; 60,88</t>
+          <t>13,69; 57,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,31; 69,48</t>
+          <t>40,07; 86,59</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,85; 64,98</t>
+          <t>28,41; 67,65</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>11,55; 45,31</t>
+          <t>9,0; 45,16</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>33,54; 82,09</t>
+          <t>51,88; 95,39</t>
         </is>
       </c>
     </row>
